--- a/processo_2/synthetic_proposals/PROPOSTA_040/ficha_pontuacao.xlsx
+++ b/processo_2/synthetic_proposals/PROPOSTA_040/ficha_pontuacao.xlsx
@@ -546,13 +546,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>7</v>
       </c>
       <c r="F6" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G6" t="inlineStr"/>
     </row>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
         <v>5.5</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G7" t="inlineStr"/>
     </row>
@@ -680,17 +680,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>2</v>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G12" t="inlineStr"/>
     </row>
@@ -703,7 +703,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -726,7 +726,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -749,7 +749,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -806,7 +806,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>7489-3940</t>
+          <t>1571-5827</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -824,7 +824,7 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G21" t="inlineStr"/>
     </row>
@@ -966,17 +966,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
         <v>4</v>
       </c>
       <c r="F26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G26" t="inlineStr"/>
     </row>
@@ -989,7 +989,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1058,17 +1058,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G30" t="inlineStr"/>
     </row>
@@ -1083,7 +1083,7 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="G31" t="inlineStr"/>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1241,17 +1241,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E39" t="n">
         <v>2</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G39" t="inlineStr"/>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -1601,13 +1601,13 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E55" t="n">
         <v>50</v>
       </c>
       <c r="F55" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G55" t="inlineStr"/>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -1668,7 +1668,7 @@
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="n">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="G58" t="inlineStr"/>
     </row>
@@ -1715,13 +1715,13 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E61" t="n">
         <v>4</v>
       </c>
       <c r="F61" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G61" t="inlineStr"/>
     </row>
@@ -1851,7 +1851,7 @@
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G67" t="inlineStr"/>
     </row>
@@ -1866,7 +1866,7 @@
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="n">
-        <v>141</v>
+        <v>17</v>
       </c>
       <c r="G68" t="inlineStr"/>
     </row>
